--- a/excel/questions (1).xlsx
+++ b/excel/questions (1).xlsx
@@ -713,12 +713,12 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>image</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>media/12471037-uhd_3840_2160_24fps_3.mp4</t>
+          <t>media/Screenshot 2025-04-03 115511.png</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr"/>
